--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table22.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table22.xlsx
@@ -163,7 +163,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -390,45 +390,45 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1759,24 +1759,24 @@
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="33" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="32" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.149999999999999" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
